--- a/resources/Youth_beta.xlsx
+++ b/resources/Youth_beta.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Email</t>
   </si>
@@ -54,6 +54,18 @@
   </si>
   <si>
     <t>AdaWindler@yopmail.com</t>
+  </si>
+  <si>
+    <t>JonahBarton@yopmail.com</t>
+  </si>
+  <si>
+    <t>MittieHartmann@yopmail.com</t>
+  </si>
+  <si>
+    <t>ChaunceyStoltenberg@yopmail.com</t>
+  </si>
+  <si>
+    <t>FidelHahn@yopmail.com</t>
   </si>
 </sst>
 </file>
@@ -528,7 +540,7 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1213,7 +1225,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1221,44 +1233,64 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:1">
       <c r="A2" t="s" s="0">
         <v>1</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:1">
       <c r="A3" t="s" s="0">
         <v>2</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:1">
       <c r="A4" t="s" s="0">
         <v>3</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:1">
       <c r="A5" t="s" s="0">
         <v>4</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:1">
       <c r="A6" t="s" s="0">
         <v>5</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:1">
       <c r="A7" t="s" s="0">
         <v>6</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:1">
       <c r="A8" t="s" s="0">
         <v>7</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:1">
       <c r="A9" t="s" s="0">
         <v>8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/resources/Youth_beta.xlsx
+++ b/resources/Youth_beta.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>Email</t>
   </si>
@@ -66,6 +66,9 @@
   </si>
   <si>
     <t>FidelHahn@yopmail.com</t>
+  </si>
+  <si>
+    <t>AlonzoTromp@yopmail.com</t>
   </si>
 </sst>
 </file>
@@ -1225,7 +1228,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1293,6 +1296,11 @@
         <v>12</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/resources/Youth_beta.xlsx
+++ b/resources/Youth_beta.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24980" windowHeight="12240"/>
+    <workbookView windowWidth="24720" windowHeight="12200"/>
   </bookViews>
   <sheets>
     <sheet name="UserData" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>Email</t>
   </si>
@@ -53,19 +53,13 @@
     <t>LouiseLeuschke@yopmail.com</t>
   </si>
   <si>
-    <t>AdaWindler@yopmail.com</t>
+    <t>MissRomeoBerge@yopmail.com</t>
   </si>
   <si>
-    <t>JonahBarton@yopmail.com</t>
+    <t>DiedraTromp@yopmail.com</t>
   </si>
   <si>
-    <t>MittieHartmann@yopmail.com</t>
-  </si>
-  <si>
-    <t>ChaunceyStoltenberg@yopmail.com</t>
-  </si>
-  <si>
-    <t>FidelHahn@yopmail.com</t>
+    <t>CieraHuel@yopmail.com</t>
   </si>
 </sst>
 </file>
@@ -1225,8 +1219,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <dimension ref="A1:A11"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="7"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s" s="0">
@@ -1268,7 +1262,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
+    <row r="9">
       <c r="A9" t="s" s="0">
         <v>8</v>
       </c>
@@ -1283,16 +1277,6 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="0">
-        <v>12</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/resources/Youth_beta.xlsx
+++ b/resources/Youth_beta.xlsx
@@ -9,9 +9,34 @@
     <sheet name="UserData" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="YouthClubMembers" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="7">
+  <si>
+    <t>yco2606271134m2@maildrop.cc</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>yco2606271134m1@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2606271136m4@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2606271136m3@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2606271140m5@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2606271140m6@maildrop.cc</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1321,24 +1346,90 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" t="inlineStr" s="0">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" t="inlineStr" s="0">
         <is>
           <t>Youth Club Name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" t="inlineStr" s="0">
         <is>
           <t>Status</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/resources/Youth_beta.xlsx
+++ b/resources/Youth_beta.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="8">
   <si>
     <t>yco2606271134m2@maildrop.cc</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>yco2606271140m6@maildrop.cc</t>
+  </si>
+  <si>
+    <t>DonnellSwiftIV@yopmail.com</t>
   </si>
 </sst>
 </file>
@@ -1255,7 +1258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="7"/>
   <sheetData>
     <row r="1">
@@ -1333,6 +1336,11 @@
         <is>
           <t>CieraHuel@yopmail.com</t>
         </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/resources/Youth_beta.xlsx
+++ b/resources/Youth_beta.xlsx
@@ -9,9 +9,46 @@
     <sheet name="UserData" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="YouthClubMembers" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+  <si>
+    <t>fidelbradtke@yopmail.com</t>
+  </si>
+  <si>
+    <t>philwalsh@yopmail.com</t>
+  </si>
+  <si>
+    <t>alwest@yopmail.com</t>
+  </si>
+  <si>
+    <t>ulyssesrunolfsdottirphd@yopmail.com</t>
+  </si>
+  <si>
+    <t>venadare@yopmail.com</t>
+  </si>
+  <si>
+    <t>mrdeshawnfunk@yopmail.com</t>
+  </si>
+  <si>
+    <t>kyleeroberts@yopmail.com</t>
+  </si>
+  <si>
+    <t>billifeeney@yopmail.com</t>
+  </si>
+  <si>
+    <t>jonasarmstrong@yopmail.com</t>
+  </si>
+  <si>
+    <t>adalbertohills@yopmail.com</t>
+  </si>
+  <si>
+    <t>seemahagenes@yopmail.com</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1230,7 +1267,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A22"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="7"/>
   <sheetData>
     <row r="1">
@@ -1308,6 +1345,61 @@
         <is>
           <t>CieraHuel@yopmail.com</t>
         </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1325,17 +1417,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" t="inlineStr" s="0">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" t="inlineStr" s="0">
         <is>
           <t>Youth Club Name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" t="inlineStr" s="0">
         <is>
           <t>Status</t>
         </is>
